--- a/publications.xlsx
+++ b/publications.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhanif\Documents\GitHub\publicationreporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB682A4-C57D-44DB-B762-B5BF4E273732}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37757F3-7698-447D-8875-A7BB58E8975B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1470" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Publications" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="113">
   <si>
     <t>No</t>
   </si>
@@ -343,6 +343,39 @@
   </si>
   <si>
     <t>Muneeza, A., (2026). HDFC Amna accounts for 59% of HDFC’s Q2 2026 profit, Islamic Finance News, Volume23.Issue28</t>
+  </si>
+  <si>
+    <t>International Islamic University Malaysia</t>
+  </si>
+  <si>
+    <t>Elsevier B.V.</t>
+  </si>
+  <si>
+    <t>Shamsudheen, S. V., Mohamad, S., Muneeza, A., &amp; Mahomed, Z. (2026). Ethical discourse of ethical (Islamic) finance: a systematic literature review (1988–2022) and the way forward. Journal of Islamic Accounting and Business Research, 17(7), 1324-1347.</t>
+  </si>
+  <si>
+    <t>Uddin Ahmed, M. ., &amp; Hossain, M. M. . (2026). Rationale for Islamic Banking Windows and Issues Impeding Their Effectiveness: Insights from Bangladesh. Journal of Islamic Finance, 15(1). https://journals.iium.edu.my/iiibf-journal/index.php/jif/article/view/1091</t>
+  </si>
+  <si>
+    <t>Omar, M. A., Abdel Mohsin, M. I., Beik, I. S., &amp; Mohd Zulkarnaini, S. . (2026). INCEIF Impact Index Model (IIIM) for Assessing Material and Spiritual Welfare in Islamic Social Finance. International Journal of Islamic Finance and Sustainable Development, 18(3), 117–138. https://doi.org/10.55188/ijifsd.v18i3.1392</t>
+  </si>
+  <si>
+    <t>Hamid, B. A., &amp; Haslan, A. I. N. (2026). Impediments to Optimizing Zakat Collection in Malaysia: A Bibliometric Analysis of Scholarly Literature (2011-2025). Journal of Islamic Social Finance, 4(1), 10-22.</t>
+  </si>
+  <si>
+    <t>Mahomed, Z. (2026). Supply-Side Benchmark Pricing in a Dual Banking System: Evidence from Indonesian Islamic Deposit Rates. The Quarterly Review of Economics and Finance, 102202. https://doi.org/10.1016/j.qref.2026.102202</t>
+  </si>
+  <si>
+    <t>Taylor &amp; Francis</t>
+  </si>
+  <si>
+    <t>Nazeri ANN, Mohd Nor S, Abdul-Rahman A, Ali MH (2026;), "Blockchain technology in zakat management system: potential and challenges in Malaysia". Journal of Islamic Accounting and Business Research, Vol. ahead-of-print No. ahead-of-print. https://doi.org/10.1108/JIABR-10-2024-0435</t>
+  </si>
+  <si>
+    <t>Muneeza, A. (2026). Exploring Nigeria's US dollar crisis: Economic factors, cryptocurrency influence, and Islamic economic perspectives. Qualitative Research in Financial Markets.</t>
+  </si>
+  <si>
+    <t>Mahomed, Z. (2026). Term structure inversion and monetary policy transmission in a dual banking system: Evidence from Indonesia. Emerging Markets Finance and Trade.</t>
   </si>
 </sst>
 </file>
@@ -408,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -419,7 +452,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -432,6 +464,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -735,61 +779,61 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M58"/>
+  <dimension ref="A1:M69"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6" style="6" customWidth="1"/>
-    <col min="2" max="2" width="70" style="6" customWidth="1"/>
-    <col min="3" max="3" width="14" style="6" customWidth="1"/>
-    <col min="4" max="4" width="16" style="6" customWidth="1"/>
-    <col min="5" max="7" width="8" style="6" customWidth="1"/>
-    <col min="8" max="8" width="10" style="6" customWidth="1"/>
-    <col min="9" max="9" width="14" style="6" customWidth="1"/>
-    <col min="10" max="10" width="12" style="6" customWidth="1"/>
-    <col min="11" max="11" width="16" style="6" customWidth="1"/>
-    <col min="12" max="12" width="26" style="6" customWidth="1"/>
-    <col min="13" max="13" width="16" style="6" customWidth="1"/>
-    <col min="14" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="6" style="5" customWidth="1"/>
+    <col min="2" max="2" width="70" style="5" customWidth="1"/>
+    <col min="3" max="3" width="14" style="5" customWidth="1"/>
+    <col min="4" max="4" width="16" style="5" customWidth="1"/>
+    <col min="5" max="7" width="8" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10" style="5" customWidth="1"/>
+    <col min="9" max="9" width="14" style="5" customWidth="1"/>
+    <col min="10" max="10" width="12" style="5" customWidth="1"/>
+    <col min="11" max="11" width="16" style="5" customWidth="1"/>
+    <col min="12" max="12" width="26" style="5" customWidth="1"/>
+    <col min="13" max="13" width="16" style="5" customWidth="1"/>
+    <col min="14" max="16384" width="8.7265625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -827,10 +871,10 @@
       <c r="K2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -868,10 +912,10 @@
       <c r="K3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -909,10 +953,10 @@
       <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -950,14 +994,14 @@
       <c r="K5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="50" x14ac:dyDescent="0.3">
+      <c r="M5" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -991,10 +1035,10 @@
       <c r="K6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1032,10 +1076,10 @@
       <c r="K7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1073,10 +1117,10 @@
       <c r="K8" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1114,10 +1158,10 @@
       <c r="K9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1155,10 +1199,10 @@
       <c r="K10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1196,10 +1240,10 @@
       <c r="K11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1237,10 +1281,10 @@
       <c r="K12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1278,10 +1322,10 @@
       <c r="K13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1319,10 +1363,10 @@
       <c r="K14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1360,10 +1404,10 @@
       <c r="K15" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1401,10 +1445,10 @@
       <c r="K16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1442,10 +1486,10 @@
       <c r="K17" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1483,10 +1527,10 @@
       <c r="K18" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="L18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="M18" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1524,10 +1568,10 @@
       <c r="K19" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L19" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="M19" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1565,10 +1609,10 @@
       <c r="K20" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1606,10 +1650,10 @@
       <c r="K21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1647,10 +1691,10 @@
       <c r="K22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1688,10 +1732,10 @@
       <c r="K23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1729,10 +1773,10 @@
       <c r="K24" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1770,10 +1814,10 @@
       <c r="K25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L25" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M25" s="1" t="s">
+      <c r="L25" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M25" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1811,10 +1855,10 @@
       <c r="K26" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L26" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M26" s="1" t="s">
+      <c r="L26" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M26" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1852,10 +1896,10 @@
       <c r="K27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L27" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M27" s="1" t="s">
+      <c r="L27" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M27" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1893,10 +1937,10 @@
       <c r="K28" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L28" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M28" s="1" t="s">
+      <c r="L28" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M28" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1934,10 +1978,10 @@
       <c r="K29" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M29" s="1" t="s">
+      <c r="L29" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M29" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1975,10 +2019,10 @@
       <c r="K30" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L30" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M30" s="1" t="s">
+      <c r="L30" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M30" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2016,10 +2060,10 @@
       <c r="K31" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L31" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M31" s="1" t="s">
+      <c r="L31" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M31" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2057,10 +2101,10 @@
       <c r="K32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L32" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M32" s="1" t="s">
+      <c r="L32" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M32" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2098,10 +2142,10 @@
       <c r="K33" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L33" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M33" s="1" t="s">
+      <c r="L33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M33" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2139,10 +2183,10 @@
       <c r="K34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L34" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M34" s="1" t="s">
+      <c r="L34" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M34" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2180,10 +2224,10 @@
       <c r="K35" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L35" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M35" s="1" t="s">
+      <c r="L35" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M35" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2221,10 +2265,10 @@
       <c r="K36" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L36" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M36" s="1" t="s">
+      <c r="L36" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M36" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2262,10 +2306,10 @@
       <c r="K37" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L37" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M37" s="1" t="s">
+      <c r="L37" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M37" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2303,10 +2347,10 @@
       <c r="K38" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="L38" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M38" s="1" t="s">
+      <c r="L38" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M38" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2344,10 +2388,10 @@
       <c r="K39" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L39" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M39" s="1" t="s">
+      <c r="L39" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M39" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2385,10 +2429,10 @@
       <c r="K40" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L40" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M40" s="1" t="s">
+      <c r="L40" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M40" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2426,10 +2470,10 @@
       <c r="K41" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L41" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M41" s="1" t="s">
+      <c r="L41" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M41" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2467,10 +2511,10 @@
       <c r="K42" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L42" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M42" s="1" t="s">
+      <c r="L42" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M42" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2508,10 +2552,10 @@
       <c r="K43" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L43" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M43" s="1" t="s">
+      <c r="L43" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M43" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2549,10 +2593,10 @@
       <c r="K44" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L44" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M44" s="1" t="s">
+      <c r="L44" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M44" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2590,10 +2634,10 @@
       <c r="K45" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L45" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M45" s="1" t="s">
+      <c r="L45" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M45" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2631,10 +2675,10 @@
       <c r="K46" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L46" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M46" s="1" t="s">
+      <c r="L46" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M46" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2672,10 +2716,10 @@
       <c r="K47" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L47" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M47" s="1" t="s">
+      <c r="L47" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M47" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2713,10 +2757,10 @@
       <c r="K48" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L48" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M48" s="1" t="s">
+      <c r="L48" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M48" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2754,10 +2798,10 @@
       <c r="K49" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L49" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M49" s="1" t="s">
+      <c r="L49" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M49" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2795,10 +2839,10 @@
       <c r="K50" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L50" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M50" s="1" t="s">
+      <c r="L50" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M50" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2836,10 +2880,10 @@
       <c r="K51" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L51" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M51" s="1" t="s">
+      <c r="L51" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M51" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2877,51 +2921,51 @@
       <c r="K52" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="L52" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="M52" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" s="7" customFormat="1" ht="62.5" x14ac:dyDescent="0.35">
+      <c r="L52" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="M52" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" s="6" customFormat="1" ht="62.5" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="C53" s="7" t="s">
+      <c r="C53" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D53" s="7" t="s">
+      <c r="D53" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F53" s="7" t="s">
+      <c r="F53" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G53" s="7" t="s">
+      <c r="G53" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="H53" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I53" s="7" t="s">
+      <c r="H53" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I53" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="J53" s="7" t="s">
+      <c r="J53" s="6" t="s">
         <v>14</v>
       </c>
       <c r="K53" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L53" s="8" t="s">
+      <c r="L53" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M53" s="10" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2959,10 +3003,10 @@
       <c r="K54" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="L54" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M54" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2974,7 +3018,7 @@
         <v>99</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>14</v>
@@ -3000,10 +3044,10 @@
       <c r="K55" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="L55" s="6" t="s">
+      <c r="L55" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M55" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3015,7 +3059,7 @@
         <v>100</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>14</v>
@@ -3041,10 +3085,10 @@
       <c r="K56" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="L56" s="6" t="s">
+      <c r="L56" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M56" s="10" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3052,21 +3096,406 @@
       <c r="A57" s="1">
         <v>56</v>
       </c>
-      <c r="B57" s="9" t="s">
+      <c r="B57" s="8" t="s">
         <v>101</v>
       </c>
+      <c r="C57" s="6"/>
+      <c r="D57" s="6"/>
+      <c r="E57" s="6"/>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6"/>
+      <c r="H57" s="6"/>
       <c r="I57" s="6" t="s">
         <v>22</v>
       </c>
+      <c r="J57" s="6"/>
       <c r="K57" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="M57" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B58" s="4"/>
+      <c r="L57" s="11"/>
+      <c r="M57" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="50.5" x14ac:dyDescent="0.3">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K58" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="M58" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="50.5" x14ac:dyDescent="0.3">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I59" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J59" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K59" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="M59" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="50.5" x14ac:dyDescent="0.3">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I60" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J60" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K60" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L60" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="M60" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="38" x14ac:dyDescent="0.3">
+      <c r="A61" s="1">
+        <v>60</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I61" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J61" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K61" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L61" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="M61" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="38" x14ac:dyDescent="0.3">
+      <c r="A62" s="1">
+        <v>61</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>108</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I62" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="M62" s="10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="50.5" x14ac:dyDescent="0.3">
+      <c r="A63" s="1">
+        <v>62</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H63" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I63" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J63" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K63" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L63" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M63" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="38" x14ac:dyDescent="0.3">
+      <c r="A64" s="1">
+        <v>63</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I64" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="M64" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="38" x14ac:dyDescent="0.3">
+      <c r="A65" s="1">
+        <v>64</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="I65" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K65" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="L65" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="M65" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C66" s="6"/>
+      <c r="D66" s="6"/>
+      <c r="E66" s="6"/>
+      <c r="F66" s="6"/>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C67" s="6"/>
+      <c r="D67" s="6"/>
+      <c r="E67" s="6"/>
+      <c r="F67" s="6"/>
+      <c r="G67" s="6"/>
+      <c r="H67" s="6"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C68" s="6"/>
+      <c r="D68" s="6"/>
+      <c r="E68" s="6"/>
+      <c r="F68" s="6"/>
+      <c r="G68" s="6"/>
+      <c r="H68" s="6"/>
+      <c r="I68" s="6"/>
+      <c r="J68" s="6"/>
+      <c r="K68" s="6"/>
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="C69" s="6"/>
+      <c r="D69" s="6"/>
+      <c r="E69" s="6"/>
+      <c r="F69" s="6"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6"/>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/publications.xlsx
+++ b/publications.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mhanif\Documents\GitHub\publicationreporting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37757F3-7698-447D-8875-A7BB58E8975B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DAE29E-22F0-4FCC-BFC3-BABCECEE5BEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -351,18 +351,12 @@
     <t>Elsevier B.V.</t>
   </si>
   <si>
-    <t>Shamsudheen, S. V., Mohamad, S., Muneeza, A., &amp; Mahomed, Z. (2026). Ethical discourse of ethical (Islamic) finance: a systematic literature review (1988–2022) and the way forward. Journal of Islamic Accounting and Business Research, 17(7), 1324-1347.</t>
-  </si>
-  <si>
     <t>Uddin Ahmed, M. ., &amp; Hossain, M. M. . (2026). Rationale for Islamic Banking Windows and Issues Impeding Their Effectiveness: Insights from Bangladesh. Journal of Islamic Finance, 15(1). https://journals.iium.edu.my/iiibf-journal/index.php/jif/article/view/1091</t>
   </si>
   <si>
     <t>Omar, M. A., Abdel Mohsin, M. I., Beik, I. S., &amp; Mohd Zulkarnaini, S. . (2026). INCEIF Impact Index Model (IIIM) for Assessing Material and Spiritual Welfare in Islamic Social Finance. International Journal of Islamic Finance and Sustainable Development, 18(3), 117–138. https://doi.org/10.55188/ijifsd.v18i3.1392</t>
   </si>
   <si>
-    <t>Hamid, B. A., &amp; Haslan, A. I. N. (2026). Impediments to Optimizing Zakat Collection in Malaysia: A Bibliometric Analysis of Scholarly Literature (2011-2025). Journal of Islamic Social Finance, 4(1), 10-22.</t>
-  </si>
-  <si>
     <t>Mahomed, Z. (2026). Supply-Side Benchmark Pricing in a Dual Banking System: Evidence from Indonesian Islamic Deposit Rates. The Quarterly Review of Economics and Finance, 102202. https://doi.org/10.1016/j.qref.2026.102202</t>
   </si>
   <si>
@@ -376,6 +370,12 @@
   </si>
   <si>
     <t>Mahomed, Z. (2026). Term structure inversion and monetary policy transmission in a dual banking system: Evidence from Indonesia. Emerging Markets Finance and Trade.</t>
+  </si>
+  <si>
+    <t>Hamid, B. A., &amp; Haslan, A. I. N. (2026). Impediments to Optimizing Zakat Collection in Malaysia: A Bibliometric Analysis of Scholarly Literature (2011-2025). Journal of Islamic Social Finance, 4(1), 10-22. https://journals.iium.edu.my/jisf/index.php/iiibf/article/view/67</t>
+  </si>
+  <si>
+    <t>Shamsudheen, S. V., Mohamad, S., Muneeza, A., &amp; Mahomed, Z. (2026). Ethical discourse of ethical (Islamic) finance: a systematic literature review (1988–2022) and the way forward. Journal of Islamic Accounting and Business Research, 17(7), 1324-1347. https://doi.org/10.1108/JIABR-11-2022-0315</t>
   </si>
 </sst>
 </file>
@@ -441,7 +441,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -476,6 +476,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3122,7 +3125,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C58" s="7" t="s">
         <v>20</v>
@@ -3163,7 +3166,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C59" s="7" t="s">
         <v>14</v>
@@ -3204,7 +3207,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C60" s="7" t="s">
         <v>20</v>
@@ -3240,12 +3243,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="38" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="50.5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="C61" s="7" t="s">
         <v>14</v>
@@ -3286,7 +3289,7 @@
         <v>61</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C62" s="7" t="s">
         <v>20</v>
@@ -3327,7 +3330,7 @@
         <v>62</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C63" s="7" t="s">
         <v>20</v>
@@ -3368,7 +3371,7 @@
         <v>63</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C64" s="7" t="s">
         <v>20</v>
@@ -3404,12 +3407,12 @@
         <v>54</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="38" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:13" ht="37.5" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-      <c r="B65" s="9" t="s">
-        <v>112</v>
+      <c r="B65" s="13" t="s">
+        <v>110</v>
       </c>
       <c r="C65" s="7" t="s">
         <v>20</v>
@@ -3439,7 +3442,7 @@
         <v>16</v>
       </c>
       <c r="L65" s="12" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="M65" s="12" t="s">
         <v>54</v>
